--- a/backend/exports/按到港分类货柜清单_2026-03-05.xlsx
+++ b/backend/exports/按到港分类货柜清单_2026-03-05.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56324A92-D171-4F77-A9B7-966B1E6E74FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AF67FB-F142-42EC-AA27-57D8109223CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="按到港分类货柜清单" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet1!$A$1:$CT$413</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">按到港分类货柜清单!$A$1:$K$351</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">按到港分类货柜清单!$A$1:$E$351</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -10893,7 +10893,7 @@
         <v>3407</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -10948,7 +10948,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -10976,7 +10976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -11004,7 +11004,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -11060,7 +11060,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -11088,7 +11088,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -11144,7 +11144,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -11200,7 +11200,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -11256,7 +11256,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -11312,7 +11312,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -11340,7 +11340,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -11368,7 +11368,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -11396,7 +11396,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -11424,7 +11424,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -11452,7 +11452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -11536,7 +11536,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -11564,7 +11564,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -11620,7 +11620,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -11676,7 +11676,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -11704,7 +11704,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -11760,7 +11760,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -11788,7 +11788,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -11872,7 +11872,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -11900,7 +11900,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -11928,7 +11928,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -11984,7 +11984,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -12068,7 +12068,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -12124,7 +12124,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -12152,7 +12152,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -12180,7 +12180,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:12" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>115</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>115</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>115</v>
       </c>
@@ -12371,7 +12371,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>115</v>
       </c>
@@ -12407,7 +12407,7 @@
         <v>2026-02-12 15:46:00</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>115</v>
       </c>
@@ -12499,7 +12499,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>115</v>
       </c>
@@ -12591,7 +12591,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>115</v>
       </c>
@@ -12627,7 +12627,7 @@
         <v>2026-02-12 00:00:00</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>115</v>
       </c>
@@ -12663,7 +12663,7 @@
         <v>2026-01-29 00:00:00</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>115</v>
       </c>
@@ -12699,7 +12699,7 @@
         <v>2026-02-18 15:20:00</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>115</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>2026-02-23 19:01:00</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>115</v>
       </c>
@@ -12771,7 +12771,7 @@
         <v>2026-02-11 00:00:00</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>115</v>
       </c>
@@ -12807,7 +12807,7 @@
         <v>2026-02-18 00:00:00</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>115</v>
       </c>
@@ -12843,7 +12843,7 @@
         <v>2026-02-18 00:00:00</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>115</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>2026-02-21 12:30:00</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>115</v>
       </c>
@@ -12915,7 +12915,7 @@
         <v>2026-02-14 09:58:00</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>115</v>
       </c>
@@ -12951,7 +12951,7 @@
         <v>2026-02-11 00:00:00</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>115</v>
       </c>
@@ -12987,7 +12987,7 @@
         <v>2026-02-20 07:20:00</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>115</v>
       </c>
@@ -13023,7 +13023,7 @@
         <v>2026-02-25 06:03:00</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>115</v>
       </c>
@@ -13059,7 +13059,7 @@
         <v>2026-02-12 13:35:00</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>115</v>
       </c>
@@ -13095,7 +13095,7 @@
         <v>2026-02-13 11:50:00</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>115</v>
       </c>
@@ -13131,7 +13131,7 @@
         <v>2026-02-11 06:08:00</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>115</v>
       </c>
@@ -13167,7 +13167,7 @@
         <v>2026-02-17 06:19:00</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>115</v>
       </c>
@@ -13203,7 +13203,7 @@
         <v>2026-02-16 07:56:00</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>115</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -13331,7 +13331,7 @@
         <v>2026-02-12 12:44:00</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>115</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>115</v>
       </c>
@@ -13487,7 +13487,7 @@
         <v>2026-02-26 14:27:00</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>2026-02-20 06:43:00</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>115</v>
       </c>
@@ -13615,7 +13615,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>115</v>
       </c>
@@ -13651,7 +13651,7 @@
         <v>2026-02-20 07:55:00</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>115</v>
       </c>
@@ -13687,7 +13687,7 @@
         <v>2026-02-23 15:56:00</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>115</v>
       </c>
@@ -13723,7 +13723,7 @@
         <v>2026-02-26 10:10:00</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>115</v>
       </c>
@@ -13759,7 +13759,7 @@
         <v>2026-02-26 14:51:00</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>115</v>
       </c>
@@ -13851,7 +13851,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>115</v>
       </c>
@@ -13887,7 +13887,7 @@
         <v>2026-02-23 07:06:00</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>115</v>
       </c>
@@ -13951,7 +13951,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
         <v>115</v>
       </c>
@@ -13987,7 +13987,7 @@
         <v>2026-02-21 08:35:00</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
         <v>115</v>
       </c>
@@ -14023,7 +14023,7 @@
         <v>2026-02-24 09:07:00</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -14059,7 +14059,7 @@
         <v>2026-02-20 13:22:00</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
         <v>115</v>
       </c>
@@ -14095,7 +14095,7 @@
         <v>2026-02-26 10:34:00</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
         <v>115</v>
       </c>
@@ -14215,7 +14215,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
         <v>115</v>
       </c>
@@ -14251,7 +14251,7 @@
         <v>2026-02-20 00:00:00</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
         <v>115</v>
       </c>
@@ -14287,7 +14287,7 @@
         <v>2026-02-18 00:00:00</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
         <v>115</v>
       </c>
@@ -14323,7 +14323,7 @@
         <v>2026-02-24 16:51:19</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
         <v>115</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>2026-02-26 08:06:00</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -14395,7 +14395,7 @@
         <v>2026-02-20 07:31:00</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>115</v>
       </c>
@@ -14431,7 +14431,7 @@
         <v>2026-01-30 17:12:00</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -14467,7 +14467,7 @@
         <v>2026-02-21 13:20:00</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>115</v>
       </c>
@@ -14503,7 +14503,7 @@
         <v>2026-02-25 06:06:00</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>115</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>115</v>
       </c>
@@ -14603,7 +14603,7 @@
         <v>2026-02-15 07:13:00</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>115</v>
       </c>
@@ -14639,7 +14639,7 @@
         <v>2026-02-24 07:09:00</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>115</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>115</v>
       </c>
@@ -14739,7 +14739,7 @@
         <v>2026-02-24 16:45:57</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>115</v>
       </c>
@@ -14775,7 +14775,7 @@
         <v>2026-02-24 16:50:19</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>115</v>
       </c>
@@ -14811,7 +14811,7 @@
         <v>2026-02-16 07:41:00</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>115</v>
       </c>
@@ -14903,7 +14903,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
         <v>115</v>
       </c>
@@ -14967,7 +14967,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" t="s">
         <v>115</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
         <v>115</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>2026-02-19 12:30:00</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
         <v>115</v>
       </c>
@@ -15103,7 +15103,7 @@
         <v>2026-02-20 19:05:00</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
         <v>115</v>
       </c>
@@ -15139,7 +15139,7 @@
         <v>2026-02-16 08:51:00</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
         <v>115</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>2026-02-21 06:14:00</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" t="s">
         <v>115</v>
       </c>
@@ -15239,7 +15239,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" t="s">
         <v>115</v>
       </c>
@@ -15275,7 +15275,7 @@
         <v>2026-01-27 13:44:00</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" t="s">
         <v>115</v>
       </c>
@@ -15311,7 +15311,7 @@
         <v>2026-02-26 12:31:00</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
         <v>115</v>
       </c>
@@ -15347,7 +15347,7 @@
         <v>2026-02-21 12:31:00</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" t="s">
         <v>115</v>
       </c>
@@ -15411,7 +15411,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" t="s">
         <v>115</v>
       </c>
@@ -15503,7 +15503,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" t="s">
         <v>115</v>
       </c>
@@ -15567,7 +15567,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" t="s">
         <v>115</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>2026-02-18 00:00:00</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" t="s">
         <v>115</v>
       </c>
@@ -15639,7 +15639,7 @@
         <v>2026-02-11 00:00:00</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A151" t="s">
         <v>115</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>2026-02-26 00:00:00</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A152" t="s">
         <v>115</v>
       </c>
@@ -15711,7 +15711,7 @@
         <v>2026-02-02 13:11:00</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" t="s">
         <v>115</v>
       </c>
@@ -15747,7 +15747,7 @@
         <v>2026-02-18 13:53:00</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
         <v>115</v>
       </c>
@@ -15783,7 +15783,7 @@
         <v>2026-02-26 07:39:00</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" t="s">
         <v>115</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>2026-02-13 06:39:00</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -15855,7 +15855,7 @@
         <v>2026-02-18 05:52:00</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A157" t="s">
         <v>115</v>
       </c>
@@ -15891,7 +15891,7 @@
         <v>2026-02-26 12:48:00</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A158" t="s">
         <v>115</v>
       </c>
@@ -15927,7 +15927,7 @@
         <v>2026-02-13 08:52:00</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" t="s">
         <v>115</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>2026-02-12 05:42:00</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" t="s">
         <v>115</v>
       </c>
@@ -16027,7 +16027,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" t="s">
         <v>115</v>
       </c>
@@ -16091,7 +16091,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" t="s">
         <v>115</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" t="s">
         <v>115</v>
       </c>
@@ -16275,7 +16275,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" t="s">
         <v>115</v>
       </c>
@@ -16339,7 +16339,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" t="s">
         <v>115</v>
       </c>
@@ -16403,7 +16403,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
         <v>115</v>
       </c>
@@ -16439,7 +16439,7 @@
         <v>2026-02-06 00:00:00</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" t="s">
         <v>115</v>
       </c>
@@ -16475,7 +16475,7 @@
         <v>2026-02-17 00:00:00</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" t="s">
         <v>115</v>
       </c>
@@ -16539,7 +16539,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" t="s">
         <v>115</v>
       </c>
@@ -16603,7 +16603,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A180" t="s">
         <v>115</v>
       </c>
@@ -16639,7 +16639,7 @@
         <v>2026-01-30 19:25:00</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A181" t="s">
         <v>115</v>
       </c>
@@ -16675,7 +16675,7 @@
         <v>2026-02-16 07:08:00</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A182" t="s">
         <v>115</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>2026-02-18 13:48:00</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A183" t="s">
         <v>115</v>
       </c>
@@ -16747,7 +16747,7 @@
         <v>2026-02-26 07:14:00</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A184" t="s">
         <v>115</v>
       </c>
@@ -16839,7 +16839,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" t="s">
         <v>115</v>
       </c>
@@ -16875,7 +16875,7 @@
         <v>2026-02-19 07:47:00</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A188" t="s">
         <v>115</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>2026-02-16 04:10:00</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A189" t="s">
         <v>115</v>
       </c>
@@ -16975,7 +16975,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A191" t="s">
         <v>115</v>
       </c>
@@ -17011,7 +17011,7 @@
         <v>2026-01-30 00:00:00</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A192" t="s">
         <v>115</v>
       </c>
@@ -17047,7 +17047,7 @@
         <v>2026-02-15 07:05:00</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A193" t="s">
         <v>115</v>
       </c>
@@ -17111,7 +17111,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A195" t="s">
         <v>115</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>2026-02-18 09:21:00</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A196" t="s">
         <v>115</v>
       </c>
@@ -17239,7 +17239,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A199" t="s">
         <v>115</v>
       </c>
@@ -17303,7 +17303,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A201" t="s">
         <v>115</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A205" t="s">
         <v>115</v>
       </c>
@@ -17487,7 +17487,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A207" t="s">
         <v>115</v>
       </c>
@@ -17523,7 +17523,7 @@
         <v>2026-02-24 10:33:00</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A208" t="s">
         <v>115</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>2026-02-24 05:29:00</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A209" t="s">
         <v>115</v>
       </c>
@@ -17595,7 +17595,7 @@
         <v>2026-02-20 05:09:00</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A210" t="s">
         <v>115</v>
       </c>
@@ -17631,7 +17631,7 @@
         <v>2026-02-12 07:10:00</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A211" t="s">
         <v>115</v>
       </c>
@@ -17667,7 +17667,7 @@
         <v>2026-02-10 00:00:00</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A212" t="s">
         <v>115</v>
       </c>
@@ -17703,7 +17703,7 @@
         <v>2026-02-10 00:00:00</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A213" t="s">
         <v>115</v>
       </c>
@@ -17739,7 +17739,7 @@
         <v>2026-02-21 08:50:00</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A214" t="s">
         <v>115</v>
       </c>
@@ -17775,7 +17775,7 @@
         <v>2026-02-11 00:00:00</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A215" t="s">
         <v>115</v>
       </c>
@@ -17867,7 +17867,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A218" t="s">
         <v>115</v>
       </c>
@@ -17903,7 +17903,7 @@
         <v>2026-02-19 00:00:00</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A219" t="s">
         <v>115</v>
       </c>
@@ -17939,7 +17939,7 @@
         <v>2026-02-26 06:20:00</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
       <c r="A220" t="s">
         <v>115</v>
       </c>
@@ -17975,7 +17975,7 @@
         <v>2026-02-16 04:31:00</v>
       </c>
     </row>
-    <row r="221" spans="1:12" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A221" s="2" t="s">
         <v>484</v>
       </c>
@@ -17999,7 +17999,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A222" t="s">
         <v>484</v>
       </c>
@@ -18024,7 +18024,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A223" t="s">
         <v>484</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A224" t="s">
         <v>484</v>
       </c>
@@ -18074,7 +18074,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A225" t="s">
         <v>484</v>
       </c>
@@ -18099,7 +18099,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A226" t="s">
         <v>484</v>
       </c>
@@ -18124,7 +18124,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A227" t="s">
         <v>484</v>
       </c>
@@ -18149,7 +18149,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A228" t="s">
         <v>484</v>
       </c>
@@ -18174,7 +18174,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A229" t="s">
         <v>484</v>
       </c>
@@ -18199,7 +18199,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A230" t="s">
         <v>484</v>
       </c>
@@ -18224,7 +18224,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A231" t="s">
         <v>484</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A232" t="s">
         <v>484</v>
       </c>
@@ -18274,7 +18274,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A233" t="s">
         <v>484</v>
       </c>
@@ -18299,7 +18299,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A234" t="s">
         <v>484</v>
       </c>
@@ -18324,7 +18324,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A235" t="s">
         <v>484</v>
       </c>
@@ -18349,7 +18349,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A236" t="s">
         <v>484</v>
       </c>
@@ -18374,7 +18374,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A237" t="s">
         <v>484</v>
       </c>
@@ -18399,7 +18399,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A238" t="s">
         <v>484</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A239" t="s">
         <v>484</v>
       </c>
@@ -18449,7 +18449,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A240" t="s">
         <v>484</v>
       </c>
@@ -18474,7 +18474,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A241" t="s">
         <v>484</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A242" t="s">
         <v>484</v>
       </c>
@@ -18524,7 +18524,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A243" t="s">
         <v>484</v>
       </c>
@@ -18549,7 +18549,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A244" t="s">
         <v>484</v>
       </c>
@@ -18574,7 +18574,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A245" t="s">
         <v>484</v>
       </c>
@@ -18599,7 +18599,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A246" t="s">
         <v>484</v>
       </c>
@@ -18624,7 +18624,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A247" t="s">
         <v>484</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A248" t="s">
         <v>484</v>
       </c>
@@ -18674,7 +18674,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A249" t="s">
         <v>484</v>
       </c>
@@ -18699,7 +18699,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A250" t="s">
         <v>484</v>
       </c>
@@ -18724,7 +18724,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A251" t="s">
         <v>484</v>
       </c>
@@ -18749,7 +18749,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A252" t="s">
         <v>484</v>
       </c>
@@ -18774,7 +18774,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A253" t="s">
         <v>484</v>
       </c>
@@ -18799,7 +18799,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A254" t="s">
         <v>484</v>
       </c>
@@ -18824,7 +18824,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A255" t="s">
         <v>484</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A256" t="s">
         <v>484</v>
       </c>
@@ -18874,7 +18874,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A257" t="s">
         <v>484</v>
       </c>
@@ -18899,7 +18899,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A258" t="s">
         <v>484</v>
       </c>
@@ -18924,7 +18924,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A259" t="s">
         <v>484</v>
       </c>
@@ -18949,7 +18949,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A260" t="s">
         <v>484</v>
       </c>
@@ -18974,7 +18974,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A261" t="s">
         <v>484</v>
       </c>
@@ -18999,7 +18999,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A262" t="s">
         <v>484</v>
       </c>
@@ -19024,7 +19024,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A263" t="s">
         <v>484</v>
       </c>
@@ -19049,7 +19049,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A264" t="s">
         <v>484</v>
       </c>
@@ -19074,7 +19074,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A265" t="s">
         <v>484</v>
       </c>
@@ -19099,7 +19099,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A266" t="s">
         <v>484</v>
       </c>
@@ -21248,10 +21248,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K351" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
+  <autoFilter ref="A1:E351" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
       <filters>
-        <filter val="已还箱"/>
+        <filter val="at_port"/>
       </filters>
     </filterColumn>
   </autoFilter>
